--- a/SMO/TemplateExcel/Export_Data_Struct_Draft.xlsx
+++ b/SMO/TemplateExcel/Export_Data_Struct_Draft.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D2S Project Github\PMS-FECON-GD2\SMO\TemplateExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCEAE20-FBA8-4390-8DC0-B5199A01F42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CAEA0B-10E0-4BE1-8F49-89E4738A3432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cấu trúc Chi Phí" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -43,15 +43,6 @@
   </si>
   <si>
     <t>Khối lượng</t>
-  </si>
-  <si>
-    <t>Loại</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Hạng mục</t>
   </si>
   <si>
     <t>Đơn vị tính</t>
@@ -99,6 +90,57 @@
   <si>
     <t>DỮ LIỆU CÂY CẤU TRÚC CHI PHÍ</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hạng mục </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Code</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> *</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Loại </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Lưu ý: Không được thêm sửa xoá các trường thông tin đánh dấu * việc làm này sẽ ảnh hưởng đến cấu trúc cây và gây lỗi hệ thống!</t>
+  </si>
 </sst>
 </file>
 
@@ -107,7 +149,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +199,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -240,11 +290,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -259,8 +309,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -671,14 +721,16 @@
   <sheetData>
     <row r="2" spans="1:10" ht="16.8" x14ac:dyDescent="0.3">
       <c r="D2" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="12"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="H2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
@@ -687,20 +739,20 @@
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+    </row>
+    <row r="4" spans="1:10" s="3" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
       <c r="F4"/>
-      <c r="G4" s="10"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5"/>
@@ -708,42 +760,42 @@
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
       <c r="F5"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="9"/>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:10" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>13</v>
+      <c r="H7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -848,8 +900,9 @@
     <row r="27" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="D2:F3"/>
+    <mergeCell ref="H2:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -868,22 +921,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>10</v>
+      <c r="A2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
